--- a/tests/fixtures/rc_automation/sample_schedule.xlsx
+++ b/tests/fixtures/rc_automation/sample_schedule.xlsx
@@ -8,12 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="INFO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="FOOTING_TYPES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="FOOTING_PLACEMENT" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="FOOTING_REBAR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="COLUMN_TYPES" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="COLUMN_PLACEMENT" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="COLUMN_REBAR" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="LEVELS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="FOOTING_TYPES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="FOOTING_PLACEMENT" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="FOOTING_REBAR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="COLUMN_TYPES" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="COLUMN_PLACEMENT" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="COLUMN_REBAR" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,190 +498,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TypeMark</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Length</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Thickness</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>CoverTop</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>CoverBottom</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>CoverSide</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Concrete</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Comments</t>
+          <t>Model</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>C32/40</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Typical internal pad</t>
+          <t>00 Ground Lvl.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>C32/40</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>C32/40</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Under twin columns</t>
+          <t>01 1st Floor Lvl.</t>
         </is>
       </c>
     </row>
@@ -695,302 +548,190 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>TypeMark</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>TypeMark</t>
+          <t>Length</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>GridX</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>GridY</t>
+          <t>Thickness</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>CoverTop</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>CoverBottom</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>CoverSide</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>TopOffset</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Outline</t>
+          <t>Comments</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F1-A1</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Foundation</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>C32/40</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>Typical internal pad</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F1-A2</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Foundation</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>C32/40</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F1-B1</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Foundation</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>C32/40</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>F2-C1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>F3-B2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>F3-P1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>12500</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>8400</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0,0; 4500,0; 4500,3000; 2250,4200; 0,3000</t>
+          <t>Under twin columns</t>
         </is>
       </c>
     </row>
@@ -1005,157 +746,137 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>TypeMark</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>GridX</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>BarType</t>
+          <t>GridY</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Diameter</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Count</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Spacing</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>ShapeCode</t>
+          <t>TopOffset</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>EndCover</t>
+          <t>Rotation</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Outline</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>F1-A1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>T16</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Bottom outer mat</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>F1-A2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>T16</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -1163,91 +884,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>F1-B1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>T12</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Top mat</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2-C1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>T12</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1255,47 +964,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3-B2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>T16</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1303,234 +1004,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3-P1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>T16</t>
-        </is>
-      </c>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>Foundation</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>T20</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>T20</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>T16</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>T16</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0,0; 4500,0; 4500,3000; 2250,4200; 0,3000</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1543,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1554,25 +1067,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Depth</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Cover</t>
+          <t>BarType</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>Diameter</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Spacing</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ShapeCode</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>EndCover</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
@@ -1581,94 +1114,474 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>T16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C32/40</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Perimeter column</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Bottom outer mat</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>T16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C32/40</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C32/40</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Top mat</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1681,308 +1594,130 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>TypeMark</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>TypeMark</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>GridX</t>
+          <t>Depth</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>GridY</t>
+          <t>Cover</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>BaseLevel</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>BaseOffset</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>TopLevel</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>TopOffset</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Rotation</t>
+          <t>Comments</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C1-A1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>600</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>C32/40</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Perimeter column</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C1-A2</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>C32/40</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C1-B1</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>C2-C1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>C3-B2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>C32/40</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Internal</t>
         </is>
       </c>
     </row>
@@ -1997,6 +1732,322 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TypeMark</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>GridX</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>GridY</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>BaseLevel</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>BaseOffset</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>TopLevel</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>TopOffset</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C1-A1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C1-A2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C1-B1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C2-C1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C3-B2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
